--- a/content-files/Data.xlsx
+++ b/content-files/Data.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X17"/>
+  <dimension ref="A1:X16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -583,7 +583,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>26/08/2026 16:13:51</t>
+          <t>27/08/2026 13:45:51</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -982,7 +982,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>row2</t>
+          <t>S25FQ1B</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -997,56 +997,60 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Josh samples information about various rooms in different buildings around Berkeley in preparation for the upcoming semester. He stores the information in a DataFrame called rooms. The columns of rooms are described below:
-- id: A unique room id from Berkeley's internal database (type = np.int64).
-- building: Name of the building the room is in (type = str).
-- number: The room number listed on the door to the room (type = str).
-- college: The Berkeley college each building is associated with from the select options of: 'CoE', 'CDSS', 'CNR', and 'LNS' (type = str).
-- renovated: The year the room was last renovated (type = str). Note: Certain rooms may never have been renovated, in which case renovated will contain a value of None.
-The first five rows of rooms are shown below:
-id | building | number | college | renovated
-100100 | Evans | 0060 | LNS | 2014
-102101 | Evans | 0010 | LNS | None
-140144 | Soda | 320 | CDSS | 2021
-310523 | Gateway | 101 | CDSS | 2025
-668377 | Cory | 540AB | CoE | 2002</t>
+          <t>Josh samples information about various rooms in different buildings around Berkeley in preparation for the upcoming semester. He stores the information in a DataFrame called rooms. The columns of rooms are described below: 
+        • id: A unique room id from Berkeley’s internal database (type = np.int64). 
+        • building: Name of the building the room is in (type = str). 
+        • number: The room number listed on the door to the room (type = str). 
+        • college: The Berkeley college each building is associated with from the select options of: 'CoE', 'CDSS', 'CNR', and 'LNS' (type = str). 
+        • renovated: The year the room was last renovated (type = str). 
+Note: Certain rooms may never have been renovated, in which case renovated will contain a value of None. The first five rows of rooms are shown below:</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>https://i.postimg.cc/KvGBp08R/Screenshot-2026-06-09-at-3-17-57-PM.png</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>https://ds100.org/su26/assets/exams/fa25/fa25_mt1_sol.pdf</t>
+          <t>https://ds100.org/sp26/assets/exams/fa25/fa25_final_sol.pdf</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Regex</t>
+          <t>Pandas</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Regex</t>
+          <t>Pandas</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>https://ds100.org/su26/assets/exams/fa25/fa25_mt1_sol.pdf</t>
+          <t>https://ds100.org/sp26/assets/exams/fa25/fa25_final_sol.pdf</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>https://cahlr.github.io/OATutor-Content-Staging/#/debug/aef2469row2</t>
+          <t>https://cahlr.github.io/OATutor-Content-Staging/#/debug/aef2469S25FQ1B</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>aef2469row2</t>
+          <t>aef2469S25FQ1B</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0e9db93f666601f1508549da395d9b49</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>row2</t>
+          <t>S25FQ1B</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1056,35 +1060,39 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fill in blank (i):</t>
+          <t>Fill in the blank (i)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Some of the values in the number column have leading zeroes (e.g., "06A"). Write a regular expression to remove all leading zeroes from the entries in the number column. Every string in number starts with a non-negative count of leading zeroes, followed by a combination of numbers and/or letters. No room number consists of only zeroes. The table below provides test cases and expected outputs for your code.
-number | extracted
-0060 | 60
-320 | 320
-00000B12 | B12
-Fill in the regex pattern below to accomplish this.
-rooms['numbe`r'] = rooms['`numbe`r'].str.extract(r'`\_\_\_\_(i)\_\_\_\_')</t>
+          <t xml:space="preserve">Josh wants to determine which colleges have the most modern buildings. A building is considered modern if at least 80% of its rooms in rooms with recorded renovations were renovated in the year 2003 or later. </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>`0*([\dA-z]+)`</t>
+          <t>rooms[~rooms["renovated"].isna()]</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>string</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>https://i.postimg.cc/L8hf2hfp/Screenshot-2026-06-09-at-3-18-04-PM.png</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>3ae9ad14ed37e14ab18440b129a9b340</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>row2</t>
+          <t>S25FQ1B</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1094,12 +1102,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Understanding the Problem</t>
+          <t>Understanding the DataFrame</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>The task is to remove leading zeroes from the room numbers in the 'number' column. Each room number starts with zero or more zeroes, followed by a combination of numbers and/or letters.</t>
+          <t>Look at the 'renovated' column in the DataFrame. Some entries are 'None', which means those rooms have never been renovated.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1121,7 +1129,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>row2</t>
+          <t>S25FQ1B</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1131,12 +1139,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Regular Expression Basics</t>
+          <t>Filtering Non-Renovated Rooms</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>A regular expression (regex) is a sequence of characters that define a search pattern. In this case, we need a pattern that matches leading zeroes and captures the rest of the string.</t>
+          <t>To focus on rooms with renovation data, you need to remove rows where 'renovated' is 'None'.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1163,27 +1171,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>row2</t>
+          <t>S25FQ1B</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Capturing Groups</t>
+          <t>Removing Non-Renovated Rooms</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>In regex, parentheses are used to create capturing groups. These groups allow us to extract specific parts of the matched string. We need to capture the part of the string after the leading zeroes.</t>
+          <t>Use the DataFrame method to filter out rows where 'renovated' is 'None'.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>rooms[~rooms['renovated'].isna()]</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>algebra</t>
+          <t>string</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1205,7 +1218,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>row2</t>
+          <t>S25FQ1B</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1215,12 +1228,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Matching Leading Zeroes</t>
+          <t>Using the isna() Method</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>The pattern '0*' matches zero or more zeroes at the start of the string. We need to follow this with a capturing group for the rest of the string.</t>
+          <t>The 'isna()' method helps identify 'None' values in a DataFrame. Use it to filter out unwanted rows.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1235,57 +1248,10 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>h3</t>
+          <t>h2</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
-        <is>
-          <t>openai</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>row2</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>scaffold</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Constructing the Regex Pattern</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Combine the pattern for matching leading zeroes with a capturing group for the rest of the string. Use '0*' to match leading zeroes and '([\dA-z]+)' to capture the rest.</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0*([\dA-z]+)</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>h5</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>h4</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
         <is>
           <t>openai</t>
         </is>
@@ -1302,7 +1268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X12"/>
+  <dimension ref="A1:X13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1491,7 +1457,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>26/08/2026 16:13:51</t>
+          <t>27/08/2026 13:45:51</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1828,7 +1794,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>row1</t>
+          <t>S25FQ1B</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1838,17 +1804,18 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Annual Dose of Regex</t>
+          <t>Making room for pandas</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Consider the following sentence:
-"It has been 71 years since the year 1954."
-For each of the regular expressions in the table below, write the matching substring(s) from the provided sentence. Make sure to write substring matches in the order they appear in the text.
-- The first matching substring should go under Match 1, the second matching substring under Match 2, and the third matching substring under Match 3.
-- If there are no matches, write NA in all three boxes. If there is only one match, write NA in the Match 2 and Match 3 boxes. If there are only two matches, write NA in the Match 3 box.
-Example (format of the answer table): for the regex be.n the matches are Match 1 = been, Match 2 = NA, Match 3 = NA. For the regex y. the matches are Match 1 = ye, Match 2 = ye, Match 3 = NA.</t>
+          <t>Josh samples information about various rooms in different buildings around Berkeley in preparation for the upcoming semester. He stores the information in a DataFrame called rooms. The columns of rooms are described below: 
+        • id: A unique room id from Berkeley’s internal database (type = np.int64). 
+        • building: Name of the building the room is in (type = str). 
+        • number: The room number listed on the door to the room (type = str). 
+        • college: The Berkeley college each building is associated with from the select options of: 'CoE', 'CDSS', 'CNR', and 'LNS' (type = str). 
+        • renovated: The year the room was last renovated (type = str). 
+Note: Certain rooms may never have been renovated, in which case renovated will contain a value of None. The first five rows of rooms are shown below:</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -1856,26 +1823,30 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>https://i.postimg.cc/KvGBp08R/Screenshot-2026-06-09-at-3-17-57-PM.png</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://ds100.org/su26/assets/exams/fa25/fa25_mt1_sol.pdf</t>
+          <t>https://ds100.org/sp26/assets/exams/fa25/fa25_final_sol.pdf</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Regex</t>
+          <t>Pandas</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Regex</t>
+          <t>Pandas</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>https://ds100.org/su26/assets/exams/fa25/fa25_mt1_sol.pdf</t>
+          <t>https://ds100.org/sp26/assets/exams/fa25/fa25_final_sol.pdf</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1884,16 +1855,20 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr">
         <is>
-          <t>https://cahlr.github.io/OATutor-Content-Staging/#/debug/a56276arow1</t>
+          <t>https://cahlr.github.io/OATutor-Content-Staging/#/debug/a56276aS25FQ1B</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>a56276arow1</t>
+          <t>a56276aS25FQ1B</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0e9db93f666601f1508549da395d9b49</t>
+        </is>
+      </c>
       <c r="X8" t="inlineStr">
         <is>
           <t>fixedProblemOrder: true</t>
@@ -1903,7 +1878,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>row1</t>
+          <t>S25FQ1B</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1913,17 +1888,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>\d+</t>
+          <t>Fill in the blank (ii)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>For each regular expression, write the matching substring(s) from the sentence "It has been 71 years since the year 1954." in the order they appear: Match 1, Match 2, Match 3. Write NA in any box that has no match.</t>
+          <t xml:space="preserve">Josh wants to determine which colleges have the most modern buildings. A building is considered modern if at least 80% of its rooms in rooms with recorded renovations were renovated in the year 2003 or later. </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>71, 1954, NA</t>
+          <t>lambda sf: (sum(sf["renovated"].astype(int) &gt;= 2003) / sf["renovated"].size) &gt;= 0.80</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1934,7 +1909,11 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>https://i.postimg.cc/L8hf2hfp/Screenshot-2026-06-09-at-3-18-04-PM.png</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
@@ -1947,7 +1926,11 @@
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>3ae9ad14ed37e14ab18440b129a9b340</t>
+        </is>
+      </c>
       <c r="X9" t="inlineStr">
         <is>
           <t>chat_display_mode: Off</t>
@@ -1957,7 +1940,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>row1</t>
+          <t>S25FQ1B</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1967,18 +1950,18 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Understanding the Regex</t>
+          <t>Understanding the Filter Condition</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>The regular expression \d+ is used to match one or more digits in a sequence. In the sentence, look for any numbers.</t>
+          <t>To determine if a building is modern, we need to check if at least 80% of its rooms were renovated in 2003 or later. How can you express this condition using a lambda function?</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>algebra</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2011,32 +1994,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>row1</t>
+          <t>S25FQ1B</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Identify the Matches</t>
+          <t>Using the Renovated Column</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Identify the numbers in the sentence "It has been 71 years since the year 1954." that match the regex \d+.</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>71, 1954, NA</t>
-        </is>
-      </c>
+          <t>Consider how you can use the 'renovated' column to filter rooms. What operation can you perform to check if the renovation year is 2003 or later?</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>algebra</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2044,11 +2023,7 @@
           <t>h2</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
@@ -2073,28 +2048,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>row1</t>
+          <t>S25FQ1B</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hint</t>
+          <t>scaffold</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Order of Matches</t>
+          <t>Calculate the Proportion of Modern Rooms</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Remember to list the matches in the order they appear in the sentence. If there are no more matches, fill the remaining boxes with NA.</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
+          <t>How can you calculate the proportion of rooms renovated in 2003 or later? Use the sum of rooms renovated in 2003 or later divided by the total number of rooms with recorded renovations.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>sum(sf['renovated'].astype(int)&gt;=2003)/sf['renovated'].size</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>numeric</t>
+          <t>string</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2104,7 +2083,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>h2</t>
+          <t>h1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2128,6 +2107,68 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>S25FQ1B</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>scaffold</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Check the Modern Condition</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>How can you check if the proportion of modern rooms is at least 80%?</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>(sum(sf['renovated'].astype(int)&gt;=2003)/sf['renovated'].size)&gt;=0.80</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>h4</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>h3</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
